--- a/04_Output/2026_Hg_SS_Final_FCAs.xlsx
+++ b/04_Output/2026_Hg_SS_Final_FCAs.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Original" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Original!$A$1:$U$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ready for TAC'!$A$1:$W$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Original!$A$1:$U$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ready for TAC'!$A$1:$W$32</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="88">
   <si>
     <t>Waterbody</t>
   </si>
@@ -109,9 +109,6 @@
     <t>mg/Kg</t>
   </si>
   <si>
-    <t>Any</t>
-  </si>
-  <si>
     <t>WCBA</t>
   </si>
   <si>
@@ -293,17 +290,27 @@
   </si>
   <si>
     <t>Big Creek Lakes</t>
+  </si>
+  <si>
+    <t>any</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -385,39 +392,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD8E4BC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -634,7 +635,9 @@
     <col min="1" max="1" width="46.85546875" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
     <col min="3" max="3" width="16.28515625" hidden="1" customWidth="1"/>
-    <col min="4" max="6" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="18.140625" customWidth="1"/>
     <col min="8" max="9" width="11.85546875" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="11.85546875" customWidth="1"/>
@@ -719,21 +722,21 @@
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>24</v>
@@ -742,7 +745,7 @@
         <v>0.2407</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2">
         <v>10</v>
@@ -751,16 +754,16 @@
         <v>11.023622047244089</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M2" s="2">
         <v>1</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P2" s="2">
         <v>2</v>
@@ -769,22 +772,22 @@
         <v>24</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X2" s="11"/>
       <c r="Y2" s="11"/>
@@ -798,13 +801,13 @@
     </row>
     <row r="3" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -813,7 +816,7 @@
         <v>0.2407</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2">
         <v>10</v>
@@ -822,16 +825,16 @@
         <v>11.023622047244089</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M3" s="2">
         <v>3</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P3" s="2">
         <v>8</v>
@@ -840,22 +843,22 @@
         <v>24</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X3" s="11"/>
       <c r="Y3" s="11"/>
@@ -869,13 +872,13 @@
     </row>
     <row r="4" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
@@ -884,7 +887,7 @@
         <v>0.2407</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2">
         <v>10</v>
@@ -893,37 +896,37 @@
         <v>11.023622047244089</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M4" s="2">
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="T4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
@@ -937,13 +940,13 @@
     </row>
     <row r="5" spans="1:32" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
@@ -952,7 +955,7 @@
         <v>0.21698000000000001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2">
         <v>10</v>
@@ -962,40 +965,40 @@
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5" s="2">
         <v>3</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="V5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
@@ -1009,13 +1012,13 @@
     </row>
     <row r="6" spans="1:32" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>24</v>
@@ -1024,7 +1027,7 @@
         <v>0.21698000000000001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2">
         <v>10</v>
@@ -1034,40 +1037,40 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M6" s="2">
         <v>8</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="V6" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
@@ -1081,13 +1084,13 @@
     </row>
     <row r="7" spans="1:32" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>24</v>
@@ -1096,7 +1099,7 @@
         <v>0.21698000000000001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" s="2">
         <v>10</v>
@@ -1106,40 +1109,40 @@
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M7" s="2">
         <v>1</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="V7" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
@@ -1153,13 +1156,13 @@
     </row>
     <row r="8" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>24</v>
@@ -1168,7 +1171,7 @@
         <v>0.82425001125000008</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="6">
         <v>4</v>
@@ -1178,11 +1181,11 @@
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="6" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8" s="6">
         <v>0.5</v>
@@ -1200,22 +1203,22 @@
         <v>24</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V8" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W8" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
@@ -1229,13 +1232,13 @@
     </row>
     <row r="9" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -1244,7 +1247,7 @@
         <v>0.82425001125000008</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>4</v>
@@ -1254,11 +1257,11 @@
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M9" s="6">
         <v>2</v>
@@ -1276,22 +1279,22 @@
         <v>24</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>24</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W9" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
@@ -1305,7 +1308,7 @@
     </row>
     <row r="10" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>22</v>
@@ -1329,16 +1332,16 @@
         <v>20.295275589999999</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M10" s="2">
         <v>1</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P10" s="2">
         <v>3</v>
@@ -1347,19 +1350,19 @@
         <v>24</v>
       </c>
       <c r="R10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="U10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="U10" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="V10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W10" s="12" t="s">
         <v>84</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>85</v>
       </c>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
@@ -1373,7 +1376,7 @@
     </row>
     <row r="11" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>22</v>
@@ -1397,16 +1400,16 @@
         <v>20.295275589999999</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M11" s="2">
         <v>4</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P11" s="2">
         <v>8</v>
@@ -1415,19 +1418,19 @@
         <v>24</v>
       </c>
       <c r="R11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="U11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="U11" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="V11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W11" s="12" t="s">
         <v>84</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>85</v>
       </c>
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="12" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>22</v>
@@ -1456,7 +1459,7 @@
         <v>0.27707272509090908</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2">
         <v>11</v>
@@ -1465,16 +1468,16 @@
         <v>30.62992126</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M12" s="2">
         <v>2</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P12" s="2">
         <v>3</v>
@@ -1483,16 +1486,16 @@
         <v>24</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W12" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
@@ -1506,13 +1509,13 @@
     </row>
     <row r="13" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>24</v>
@@ -1521,7 +1524,7 @@
         <v>0.2217333329333333</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" s="2">
         <v>15</v>
@@ -1530,16 +1533,16 @@
         <v>15.27559055</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M13" s="2">
         <v>3</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P13" s="2">
         <v>4</v>
@@ -1548,16 +1551,16 @@
         <v>24</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W13" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
@@ -1571,13 +1574,13 @@
     </row>
     <row r="14" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>24</v>
@@ -1586,7 +1589,7 @@
         <v>0.79624467790425535</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="6">
         <v>94</v>
@@ -1598,11 +1601,11 @@
         <v>12.15984664856609</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M14" s="6">
         <v>2</v>
@@ -1620,18 +1623,18 @@
         <v>24</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
       <c r="U14" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="W14" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="W14" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
@@ -1645,13 +1648,13 @@
     </row>
     <row r="15" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>24</v>
@@ -1660,7 +1663,7 @@
         <v>0.2217333329333333</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" s="2">
         <v>15</v>
@@ -1669,31 +1672,31 @@
         <v>15.27559055</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M15" s="2">
         <v>8</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W15" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
@@ -1707,7 +1710,7 @@
     </row>
     <row r="16" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>22</v>
@@ -1722,7 +1725,7 @@
         <v>0.27924588270588241</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G16" s="2">
         <v>85</v>
@@ -1731,16 +1734,16 @@
         <v>16.062992130000001</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M16" s="2">
         <v>2</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P16" s="2">
         <v>3</v>
@@ -1749,13 +1752,13 @@
         <v>24</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W16" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W16" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
@@ -1769,13 +1772,13 @@
     </row>
     <row r="17" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>24</v>
@@ -1784,21 +1787,21 @@
         <v>0.54806000142</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G17" s="6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H17" s="6">
         <v>23.228346460000001</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="6" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M17" s="6">
         <v>0.25</v>
@@ -1816,18 +1819,18 @@
         <v>24</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
       <c r="U17" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="W17" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
@@ -1841,13 +1844,13 @@
     </row>
     <row r="18" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>24</v>
@@ -1856,7 +1859,7 @@
         <v>0.24352799812000001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" s="2">
         <v>25</v>
@@ -1865,16 +1868,16 @@
         <v>17.244094489999998</v>
       </c>
       <c r="J18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M18" s="2">
         <v>3</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P18" s="2">
         <v>4</v>
@@ -1883,13 +1886,13 @@
         <v>24</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W18" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
@@ -1903,13 +1906,13 @@
     </row>
     <row r="19" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>24</v>
@@ -1918,7 +1921,7 @@
         <v>0.24352799812000001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" s="2">
         <v>25</v>
@@ -1927,28 +1930,28 @@
         <v>17.244094489999998</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M19" s="2">
         <v>8</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W19" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W19" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
@@ -1962,13 +1965,13 @@
     </row>
     <row r="20" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>24</v>
@@ -1977,7 +1980,7 @@
         <v>0.27941666666666659</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" s="2">
         <v>12</v>
@@ -1986,16 +1989,16 @@
         <v>13.346456692913391</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M20" s="2">
         <v>2</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P20" s="2">
         <v>8</v>
@@ -2004,16 +2007,16 @@
         <v>24</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W20" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
@@ -2027,13 +2030,13 @@
     </row>
     <row r="21" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>24</v>
@@ -2042,7 +2045,7 @@
         <v>0.27941666666666659</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" s="2">
         <v>12</v>
@@ -2051,16 +2054,16 @@
         <v>13.346456692913391</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M21" s="2">
         <v>0.5</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P21" s="2">
         <v>2</v>
@@ -2069,16 +2072,16 @@
         <v>24</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W21" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
@@ -2092,13 +2095,13 @@
     </row>
     <row r="22" spans="1:32" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>24</v>
@@ -2107,7 +2110,7 @@
         <v>0.19406153846153851</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G22" s="2">
         <v>13</v>
@@ -2117,18 +2120,18 @@
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M22" s="2">
         <v>4</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P22" s="2">
         <v>8</v>
@@ -2137,18 +2140,18 @@
         <v>24</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W22" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
@@ -2162,13 +2165,13 @@
     </row>
     <row r="23" spans="1:32" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>24</v>
@@ -2177,7 +2180,7 @@
         <v>0.19406153846153851</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G23" s="2">
         <v>13</v>
@@ -2187,18 +2190,18 @@
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M23" s="2">
         <v>1</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P23" s="2">
         <v>3</v>
@@ -2207,18 +2210,18 @@
         <v>24</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W23" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
@@ -2232,13 +2235,13 @@
     </row>
     <row r="24" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>24</v>
@@ -2247,7 +2250,7 @@
         <v>0.27941666666666659</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" s="2">
         <v>12</v>
@@ -2256,31 +2259,31 @@
         <v>13.346456692913391</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M24" s="2">
         <v>8</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W24" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
@@ -2294,13 +2297,13 @@
     </row>
     <row r="25" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -2309,7 +2312,7 @@
         <v>0.16227272727272729</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G25" s="2">
         <v>11</v>
@@ -2318,16 +2321,16 @@
         <v>12.598425196850391</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M25" s="2">
         <v>1</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P25" s="2">
         <v>3</v>
@@ -2336,16 +2339,16 @@
         <v>24</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W25" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W25" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X25" s="11"/>
       <c r="Y25" s="11"/>
@@ -2359,13 +2362,13 @@
     </row>
     <row r="26" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>24</v>
@@ -2374,7 +2377,7 @@
         <v>0.1457</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G26" s="2">
         <v>11</v>
@@ -2383,16 +2386,16 @@
         <v>14.960629921259841</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M26" s="2">
         <v>1</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P26" s="2">
         <v>2</v>
@@ -2401,16 +2404,16 @@
         <v>24</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W26" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X26" s="11"/>
       <c r="Y26" s="11"/>
@@ -2424,13 +2427,13 @@
     </row>
     <row r="27" spans="1:32" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>24</v>
@@ -2439,7 +2442,7 @@
         <v>0.16227272727272729</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" s="2">
         <v>11</v>
@@ -2449,18 +2452,18 @@
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M27" s="2">
         <v>4</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P27" s="2">
         <v>8</v>
@@ -2469,18 +2472,18 @@
         <v>24</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W27" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="X27" s="11"/>
       <c r="Y27" s="11"/>
@@ -2494,34 +2497,34 @@
     </row>
     <row r="28" spans="1:32" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="D28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="8">
-        <v>0.1225409088068182</v>
+        <v>0.12524492717391311</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28" s="8">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="H28" s="8">
         <v>13.38582677</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M28" s="8">
         <v>2</v>
@@ -2539,19 +2542,19 @@
         <v>24</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="U28" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V28" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W28" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X28" s="11"/>
       <c r="Y28" s="11"/>
@@ -2565,13 +2568,13 @@
     </row>
     <row r="29" spans="1:32" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>24</v>
@@ -2580,7 +2583,7 @@
         <v>7.5408824058823529E-2</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G29" s="8">
         <v>34</v>
@@ -2589,10 +2592,10 @@
         <v>17.125984249999998</v>
       </c>
       <c r="J29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="M29" s="8">
         <v>8</v>
@@ -2610,19 +2613,19 @@
         <v>24</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T29" s="8" t="s">
         <v>24</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X29" s="11"/>
       <c r="Y29" s="11"/>
@@ -2636,13 +2639,13 @@
     </row>
     <row r="30" spans="1:32" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>24</v>
@@ -2651,7 +2654,7 @@
         <v>7.5408824058823529E-2</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G30" s="8">
         <v>34</v>
@@ -2660,10 +2663,10 @@
         <v>17.125984249999998</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M30" s="8">
         <v>3</v>
@@ -2681,19 +2684,19 @@
         <v>24</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T30" s="8" t="s">
         <v>24</v>
       </c>
       <c r="U30" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V30" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W30" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X30" s="11"/>
       <c r="Y30" s="11"/>
@@ -2707,13 +2710,13 @@
     </row>
     <row r="31" spans="1:32" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>24</v>
@@ -2722,7 +2725,7 @@
         <v>0.39292856978571428</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" s="8">
         <v>14</v>
@@ -2731,10 +2734,10 @@
         <v>29.055118109999999</v>
       </c>
       <c r="J31" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="M31" s="8">
         <v>2</v>
@@ -2752,19 +2755,19 @@
         <v>24</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T31" s="8" t="s">
         <v>24</v>
       </c>
       <c r="U31" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W31" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X31" s="11"/>
       <c r="Y31" s="11"/>
@@ -2776,7 +2779,68 @@
       <c r="AE31" s="11"/>
       <c r="AF31" s="14"/>
     </row>
-    <row r="32" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:32" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="18">
+        <v>0.27666666635185178</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="18">
+        <v>54</v>
+      </c>
+      <c r="H32" s="18">
+        <v>12.204724410000001</v>
+      </c>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="18">
+        <v>2</v>
+      </c>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P32" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="R32" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="11"/>
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11"/>
+    </row>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3734,7 +3798,7 @@
     <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:W31">
+  <autoFilter ref="A1:W32">
     <sortState ref="A2:W43">
       <sortCondition ref="W1:W43"/>
     </sortState>
@@ -3746,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA1000"/>
+  <dimension ref="A1:AC1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" customWidth="1"/>
@@ -3761,10 +3825,10 @@
     <col min="18" max="18" width="51.140625" customWidth="1"/>
     <col min="19" max="19" width="30.28515625" customWidth="1"/>
     <col min="20" max="21" width="11.85546875" customWidth="1"/>
-    <col min="22" max="27" width="14.42578125" style="14"/>
+    <col min="22" max="29" width="14.42578125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3829,237 +3893,228 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.26</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="4">
-        <v>2</v>
-      </c>
-      <c r="H2" s="4">
-        <v>17.519685039370081</v>
-      </c>
-      <c r="I2" s="4">
-        <v>16.51412564754218</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="4">
+    <row r="2" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.460666664625</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2">
+        <v>20.295275589999999</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+    </row>
+    <row r="3" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.460666664625</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2">
+        <v>20.295275589999999</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="2">
+        <v>4</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="2">
         <v>8</v>
       </c>
-      <c r="N2" s="4">
-        <v>4</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="4" t="s">
+      <c r="Q3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
+      <c r="S3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="11"/>
     </row>
-    <row r="3" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.26</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>17.519685039370081</v>
-      </c>
-      <c r="I3" s="4">
-        <v>16.51412564754218</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="4">
-        <v>3</v>
-      </c>
-      <c r="N3" s="4">
-        <v>2</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-    </row>
-    <row r="4" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="2">
-        <v>0.460666664625</v>
+        <v>0.2407</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2">
-        <v>20.295275589999999</v>
+        <v>11.023622047244089</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="2">
+      <c r="S4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+    </row>
+    <row r="5" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.2407</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2">
+        <v>11.023622047244089</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="2">
         <v>3</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-    </row>
-    <row r="5" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.460666664625</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2">
-        <v>20.295275589999999</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="2">
-        <v>4</v>
-      </c>
       <c r="O5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P5" s="2">
         <v>8</v>
@@ -4068,1928 +4123,2048 @@
         <v>24</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+    </row>
+    <row r="6" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.2407</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2">
+        <v>11.023622047244089</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
+      <c r="M6" s="2">
+        <v>8</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
     </row>
-    <row r="6" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="7" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.27707272509090908</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="G7" s="2">
+        <v>11</v>
+      </c>
+      <c r="H7" s="2">
+        <v>30.62992126</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="2">
+        <v>2</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="11"/>
+    </row>
+    <row r="8" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.12524492717391311</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="8">
+        <v>69</v>
+      </c>
+      <c r="H8" s="8">
+        <v>13.38582677</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="8">
+        <v>2</v>
+      </c>
+      <c r="N8" s="8">
         <v>1</v>
       </c>
-      <c r="H6" s="2">
-        <v>11.92913385826772</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="O8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" s="9"/>
+      <c r="T8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
+    </row>
+    <row r="9" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.2217333329333333</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="2">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2">
+        <v>15.27559055</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="2">
-        <v>2</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="2">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-    </row>
-    <row r="7" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>11.92913385826772</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-    </row>
-    <row r="8" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.2407</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="2">
-        <v>10</v>
-      </c>
-      <c r="H8" s="2">
-        <v>11.023622047244089</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-    </row>
-    <row r="9" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.2407</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="2">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2">
-        <v>11.023622047244089</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="M9" s="2">
         <v>3</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P9" s="2">
+      <c r="U9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="11"/>
+    </row>
+    <row r="10" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.2217333329333333</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="2">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2">
+        <v>15.27559055</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="2">
         <v>8</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R9" s="2" t="s">
+      <c r="O10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="11"/>
+    </row>
+    <row r="11" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.79624467790425535</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="6">
+        <v>94</v>
+      </c>
+      <c r="H11" s="6">
+        <v>15.669291339999999</v>
+      </c>
+      <c r="I11" s="6">
+        <v>12.15984664856609</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="6">
+        <v>2</v>
+      </c>
+      <c r="N11" s="6">
+        <v>3</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+    </row>
+    <row r="12" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.249</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2</v>
+      </c>
+      <c r="H12" s="8">
+        <v>7.0078740157480306</v>
+      </c>
+      <c r="I12" s="8">
+        <v>7.6323461510866739</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="8">
+        <v>1</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
+      <c r="AC12" s="11"/>
+    </row>
+    <row r="13" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.249</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2</v>
+      </c>
+      <c r="H13" s="8">
+        <v>7.0078740157480306</v>
+      </c>
+      <c r="I13" s="8">
+        <v>7.6323461510866739</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="8">
+        <v>8</v>
+      </c>
+      <c r="N13" s="8">
+        <v>4</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
+    </row>
+    <row r="14" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.249</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="8">
+        <v>2</v>
+      </c>
+      <c r="H14" s="8">
+        <v>7.0078740157480306</v>
+      </c>
+      <c r="I14" s="8">
+        <v>7.6323461510866739</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="8">
+        <v>3</v>
+      </c>
+      <c r="N14" s="8">
+        <v>1</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11"/>
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="11"/>
+    </row>
+    <row r="15" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.27924588270588241</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="2">
+        <v>85</v>
+      </c>
+      <c r="H15" s="2">
+        <v>16.062992130000001</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="2">
+        <v>2</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="11"/>
+    </row>
+    <row r="16" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="8">
+        <v>7.5408824058823529E-2</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="8">
+        <v>34</v>
+      </c>
+      <c r="H16" s="8">
+        <v>17.125984249999998</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="8">
+        <v>8</v>
+      </c>
+      <c r="N16" s="8">
+        <v>4</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P16" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" s="9"/>
+      <c r="T16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+      <c r="AB16" s="11"/>
+      <c r="AC16" s="11"/>
+    </row>
+    <row r="17" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="8">
+        <v>7.5408824058823529E-2</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="8">
+        <v>34</v>
+      </c>
+      <c r="H17" s="8">
+        <v>17.125984249999998</v>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M17" s="8">
+        <v>3</v>
+      </c>
+      <c r="N17" s="8">
+        <v>2</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" s="9"/>
+      <c r="T17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+      <c r="AB17" s="11"/>
+      <c r="AC17" s="11"/>
+    </row>
+    <row r="18" spans="1:29" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.82425001125000008</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="6">
+        <v>4</v>
+      </c>
+      <c r="H18" s="6">
+        <v>17.71653543</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="6">
+        <v>2</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="T18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
+      <c r="AB18" s="11"/>
+      <c r="AC18" s="11"/>
+    </row>
+    <row r="19" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.82425001125000008</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="6">
+        <v>4</v>
+      </c>
+      <c r="H19" s="6">
+        <v>17.71653543</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" s="6">
+        <v>2</v>
+      </c>
+      <c r="N19" s="6">
+        <v>4</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
+      <c r="AC19" s="11"/>
+    </row>
+    <row r="20" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.54806000142</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="6">
+        <v>90</v>
+      </c>
+      <c r="H20" s="6">
+        <v>23.228346460000001</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M20" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="11"/>
+    </row>
+    <row r="21" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4">
+        <v>17.519685039370081</v>
+      </c>
+      <c r="I21" s="4">
+        <v>16.51412564754218</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21" s="4">
+        <v>8</v>
+      </c>
+      <c r="N21" s="4">
+        <v>4</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
+      <c r="AC21" s="11"/>
+    </row>
+    <row r="22" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="4">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4">
+        <v>17.519685039370081</v>
+      </c>
+      <c r="I22" s="4">
+        <v>16.51412564754218</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="4">
+        <v>3</v>
+      </c>
+      <c r="N22" s="4">
+        <v>2</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="11"/>
+    </row>
+    <row r="23" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.129</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="8">
+        <v>8</v>
+      </c>
+      <c r="H23" s="8">
+        <v>15.23622047244095</v>
+      </c>
+      <c r="I23" s="8">
+        <v>16.51412564754218</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23" s="8">
+        <v>16</v>
+      </c>
+      <c r="N23" s="8">
+        <v>4</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="S23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="T23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+      <c r="AA23" s="11"/>
+      <c r="AB23" s="11"/>
+      <c r="AC23" s="11"/>
+    </row>
+    <row r="24" spans="1:29" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.16029032219354841</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="8">
+        <v>31</v>
+      </c>
+      <c r="H24" s="8">
+        <v>14.960629920000001</v>
+      </c>
+      <c r="I24" s="8">
+        <v>16.51412564754218</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="9"/>
+      <c r="L24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="8">
+        <v>4</v>
+      </c>
+      <c r="N24" s="8">
+        <v>2</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P24" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T24" s="9"/>
+      <c r="U24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
+      <c r="AB24" s="11"/>
+      <c r="AC24" s="11"/>
+    </row>
+    <row r="25" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.26</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="8">
+        <v>2</v>
+      </c>
+      <c r="H25" s="8">
+        <v>17.519685039370081</v>
+      </c>
+      <c r="I25" s="8">
+        <v>16.51412564754218</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M25" s="8">
+        <v>1</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P25" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S25" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
+      <c r="AB25" s="11"/>
+      <c r="AC25" s="11"/>
+    </row>
+    <row r="26" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.129</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="8">
+        <v>8</v>
+      </c>
+      <c r="H26" s="8">
+        <v>15.23622047244095</v>
+      </c>
+      <c r="I26" s="8">
+        <v>16.51412564754218</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="9"/>
+      <c r="L26" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M26" s="8">
+        <v>2</v>
+      </c>
+      <c r="N26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
+      <c r="Z26" s="11"/>
+      <c r="AA26" s="11"/>
+      <c r="AB26" s="11"/>
+      <c r="AC26" s="11"/>
+    </row>
+    <row r="27" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>11.92913385826772</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="2">
+        <v>2</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P27" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U9" s="2" t="s">
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+      <c r="Z27" s="11"/>
+      <c r="AA27" s="11"/>
+      <c r="AB27" s="11"/>
+      <c r="AC27" s="11"/>
+    </row>
+    <row r="28" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>11.92913385826772</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P28" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
+      <c r="Z28" s="11"/>
+      <c r="AA28" s="11"/>
+      <c r="AB28" s="11"/>
+      <c r="AC28" s="11"/>
+    </row>
+    <row r="29" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>11.92913385826772</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
+      <c r="M29" s="2">
+        <v>4</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="11"/>
+      <c r="AA29" s="11"/>
+      <c r="AB29" s="11"/>
+      <c r="AC29" s="11"/>
     </row>
-    <row r="10" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="30" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.24352799812000001</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="2">
+        <v>25</v>
+      </c>
+      <c r="H30" s="2">
+        <v>17.244094489999998</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="2">
+        <v>3</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11"/>
+      <c r="AA30" s="11"/>
+      <c r="AB30" s="11"/>
+      <c r="AC30" s="11"/>
+    </row>
+    <row r="31" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.24352799812000001</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G31" s="2">
+        <v>25</v>
+      </c>
+      <c r="H31" s="2">
+        <v>17.244094489999998</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31" s="2">
+        <v>8</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V31" s="11"/>
+      <c r="W31" s="11"/>
+      <c r="X31" s="11"/>
+      <c r="Y31" s="11"/>
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="11"/>
+      <c r="AC31" s="11"/>
+    </row>
+    <row r="32" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.27941666666666659</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="2">
+        <v>12</v>
+      </c>
+      <c r="H32" s="2">
+        <v>13.346456692913391</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="2">
+        <v>2</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P32" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="11"/>
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11"/>
+    </row>
+    <row r="33" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.27941666666666659</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="2">
+        <v>12</v>
+      </c>
+      <c r="H33" s="2">
+        <v>13.346456692913391</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P33" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V33" s="11"/>
+      <c r="W33" s="11"/>
+      <c r="X33" s="11"/>
+      <c r="Y33" s="11"/>
+      <c r="Z33" s="11"/>
+      <c r="AA33" s="11"/>
+      <c r="AB33" s="11"/>
+      <c r="AC33" s="11"/>
+    </row>
+    <row r="34" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.27707272509090908</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.19406153846153851</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="2">
+        <v>13</v>
+      </c>
+      <c r="H34" s="2">
+        <v>16.614173228346459</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="2">
+        <v>4</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V34" s="11"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="11"/>
+      <c r="Y34" s="11"/>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="11"/>
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="11"/>
+    </row>
+    <row r="35" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.19406153846153851</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" s="2">
+        <v>13</v>
+      </c>
+      <c r="H35" s="2">
+        <v>16.614173228346459</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M35" s="2">
+        <v>1</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+      <c r="Y35" s="11"/>
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11"/>
+      <c r="AB35" s="11"/>
+      <c r="AC35" s="11"/>
+    </row>
+    <row r="36" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.27941666666666659</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="2">
+        <v>12</v>
+      </c>
+      <c r="H36" s="2">
+        <v>13.346456692913391</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36" s="2">
+        <v>8</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="2">
-        <v>11</v>
-      </c>
-      <c r="H10" s="2">
-        <v>30.62992126</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V36" s="11"/>
+      <c r="W36" s="11"/>
+      <c r="X36" s="11"/>
+      <c r="Y36" s="11"/>
+      <c r="Z36" s="11"/>
+      <c r="AA36" s="11"/>
+      <c r="AB36" s="11"/>
+      <c r="AC36" s="11"/>
+    </row>
+    <row r="37" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.39292856978571428</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="8">
+        <v>14</v>
+      </c>
+      <c r="H37" s="8">
+        <v>29.055118109999999</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="2">
+      <c r="M37" s="8">
         <v>2</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-    </row>
-    <row r="11" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.16227272727272729</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="2">
-        <v>11</v>
-      </c>
-      <c r="H11" s="2">
-        <v>12.598425196850391</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P11" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-    </row>
-    <row r="12" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.1457</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="2">
-        <v>11</v>
-      </c>
-      <c r="H12" s="2">
-        <v>14.960629921259841</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="2">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P12" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-    </row>
-    <row r="13" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.16227272727272729</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="2">
-        <v>11</v>
-      </c>
-      <c r="H13" s="2">
-        <v>12.598425196850391</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="2">
-        <v>4</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" s="2">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-    </row>
-    <row r="14" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.27941666666666659</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="2">
-        <v>12</v>
-      </c>
-      <c r="H14" s="2">
-        <v>13.346456692913391</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="2">
-        <v>2</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14" s="2">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-    </row>
-    <row r="15" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.27941666666666659</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="2">
-        <v>12</v>
-      </c>
-      <c r="H15" s="2">
-        <v>13.346456692913391</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P15" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-    </row>
-    <row r="16" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.19406153846153851</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="2">
-        <v>13</v>
-      </c>
-      <c r="H16" s="2">
-        <v>16.614173228346459</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" s="2">
-        <v>4</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P16" s="2">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-    </row>
-    <row r="17" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.19406153846153851</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="2">
-        <v>13</v>
-      </c>
-      <c r="H17" s="2">
-        <v>16.614173228346459</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M17" s="2">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P17" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-    </row>
-    <row r="18" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.2217333329333333</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="2">
-        <v>15</v>
-      </c>
-      <c r="H18" s="2">
-        <v>15.27559055</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="2">
-        <v>3</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P18" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-    </row>
-    <row r="19" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.24352799812000001</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="2">
-        <v>25</v>
-      </c>
-      <c r="H19" s="2">
-        <v>17.244094489999998</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="2">
-        <v>3</v>
-      </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P19" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-    </row>
-    <row r="20" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.27924588270588241</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="2">
-        <v>85</v>
-      </c>
-      <c r="H20" s="2">
-        <v>16.062992130000001</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" s="2">
-        <v>2</v>
-      </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P20" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-    </row>
-    <row r="21" spans="1:27" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>11.92913385826772</v>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M21" s="2">
-        <v>4</v>
-      </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-    </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.2407</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="2">
-        <v>10</v>
-      </c>
-      <c r="H22" s="2">
-        <v>11.023622047244089</v>
-      </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" s="2">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-    </row>
-    <row r="23" spans="1:27" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.21698000000000001</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="2">
-        <v>10</v>
-      </c>
-      <c r="H23" s="2">
-        <v>12.99212598425197</v>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" s="2">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-    </row>
-    <row r="24" spans="1:27" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0.21698000000000001</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="2">
-        <v>10</v>
-      </c>
-      <c r="H24" s="2">
-        <v>12.99212598425197</v>
-      </c>
-      <c r="I24" s="3"/>
-      <c r="J24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M24" s="2">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-    </row>
-    <row r="25" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0.21698000000000001</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="2">
-        <v>10</v>
-      </c>
-      <c r="H25" s="2">
-        <v>12.99212598425197</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M25" s="2">
-        <v>1</v>
-      </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-    </row>
-    <row r="26" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0.27941666666666659</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G26" s="2">
-        <v>12</v>
-      </c>
-      <c r="H26" s="2">
-        <v>13.346456692913391</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" s="2">
-        <v>8</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-    </row>
-    <row r="27" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.2217333329333333</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="2">
-        <v>15</v>
-      </c>
-      <c r="H27" s="2">
-        <v>15.27559055</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M27" s="2">
-        <v>8</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
-    </row>
-    <row r="28" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0.24352799812000001</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="2">
-        <v>25</v>
-      </c>
-      <c r="H28" s="2">
-        <v>17.244094489999998</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" s="2">
-        <v>8</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-    </row>
-    <row r="29" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.82425001125000008</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" s="6">
-        <v>4</v>
-      </c>
-      <c r="H29" s="6">
-        <v>17.71653543</v>
-      </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="N29" s="6">
-        <v>2</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P29" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="R29" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="T29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-    </row>
-    <row r="30" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.82425001125000008</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" s="6">
-        <v>4</v>
-      </c>
-      <c r="H30" s="6">
-        <v>17.71653543</v>
-      </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M30" s="6">
-        <v>2</v>
-      </c>
-      <c r="N30" s="6">
-        <v>4</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P30" s="6">
-        <v>4</v>
-      </c>
-      <c r="Q30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="T30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="U30" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-    </row>
-    <row r="31" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.79624467790425535</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="6">
-        <v>94</v>
-      </c>
-      <c r="H31" s="6">
-        <v>15.669291339999999</v>
-      </c>
-      <c r="I31" s="6">
-        <v>12.15984664856609</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M31" s="6">
-        <v>2</v>
-      </c>
-      <c r="N31" s="6">
-        <v>3</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P31" s="6">
-        <v>4</v>
-      </c>
-      <c r="Q31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="R31" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-    </row>
-    <row r="32" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.54806000142</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="6">
-        <v>100</v>
-      </c>
-      <c r="H32" s="6">
-        <v>23.228346460000001</v>
-      </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M32" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="N32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Q32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="R32" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="14"/>
-      <c r="Z32" s="14"/>
-      <c r="AA32" s="14"/>
-    </row>
-    <row r="33" spans="1:27" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.129</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G33" s="8">
-        <v>8</v>
-      </c>
-      <c r="H33" s="8">
-        <v>15.23622047244095</v>
-      </c>
-      <c r="I33" s="8">
-        <v>16.51412564754218</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M33" s="8">
-        <v>16</v>
-      </c>
-      <c r="N33" s="8">
-        <v>4</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="R33" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="S33" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="T33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U33" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-    </row>
-    <row r="34" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.16029032219354841</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="8">
-        <v>31</v>
-      </c>
-      <c r="H34" s="8">
-        <v>14.960629920000001</v>
-      </c>
-      <c r="I34" s="8">
-        <v>16.51412564754218</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M34" s="8">
-        <v>4</v>
-      </c>
-      <c r="N34" s="8">
-        <v>2</v>
-      </c>
-      <c r="O34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P34" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R34" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S34" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="U34" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="14"/>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="14"/>
-    </row>
-    <row r="35" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.249</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G35" s="8">
-        <v>2</v>
-      </c>
-      <c r="H35" s="8">
-        <v>7.0078740157480306</v>
-      </c>
-      <c r="I35" s="8">
-        <v>7.6323461510866739</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M35" s="8">
-        <v>1</v>
-      </c>
-      <c r="N35" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="O35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P35" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R35" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S35" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="T35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U35" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="V35" s="14"/>
-      <c r="W35" s="14"/>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="14"/>
-      <c r="Z35" s="14"/>
-      <c r="AA35" s="14"/>
-    </row>
-    <row r="36" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.249</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G36" s="8">
-        <v>2</v>
-      </c>
-      <c r="H36" s="8">
-        <v>7.0078740157480306</v>
-      </c>
-      <c r="I36" s="8">
-        <v>7.6323461510866739</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M36" s="8">
-        <v>8</v>
-      </c>
-      <c r="N36" s="8">
-        <v>4</v>
-      </c>
-      <c r="O36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P36" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R36" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S36" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="T36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U36" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="14"/>
-      <c r="Z36" s="14"/>
-      <c r="AA36" s="14"/>
-    </row>
-    <row r="37" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.249</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="8">
-        <v>2</v>
-      </c>
-      <c r="H37" s="8">
-        <v>7.0078740157480306</v>
-      </c>
-      <c r="I37" s="8">
-        <v>7.6323461510866739</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M37" s="8">
-        <v>3</v>
       </c>
       <c r="N37" s="8">
         <v>1</v>
@@ -6004,413 +6179,469 @@
         <v>24</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="V37" s="11"/>
+      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
+      <c r="Y37" s="11"/>
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11"/>
+      <c r="AB37" s="11"/>
+      <c r="AC37" s="11"/>
+    </row>
+    <row r="38" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.16227272727272729</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="2">
+        <v>11</v>
+      </c>
+      <c r="H38" s="2">
+        <v>12.598425196850391</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="3"/>
+      <c r="O38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="T37" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
+      <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="11"/>
+      <c r="AB38" s="11"/>
+      <c r="AC38" s="11"/>
     </row>
-    <row r="38" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.26</v>
-      </c>
-      <c r="F38" s="8" t="s">
+    <row r="39" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.1457</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="2">
+        <v>11</v>
+      </c>
+      <c r="H39" s="2">
+        <v>14.960629921259841</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="2">
+        <v>1</v>
+      </c>
+      <c r="N39" s="3"/>
+      <c r="O39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V39" s="11"/>
+      <c r="W39" s="11"/>
+      <c r="X39" s="11"/>
+      <c r="Y39" s="11"/>
+      <c r="Z39" s="11"/>
+      <c r="AA39" s="11"/>
+      <c r="AB39" s="11"/>
+      <c r="AC39" s="11"/>
+    </row>
+    <row r="40" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.16227272727272729</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="2">
+        <v>11</v>
+      </c>
+      <c r="H40" s="2">
+        <v>12.598425196850391</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" s="2">
+        <v>4</v>
+      </c>
+      <c r="N40" s="3"/>
+      <c r="O40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V40" s="11"/>
+      <c r="W40" s="11"/>
+      <c r="X40" s="11"/>
+      <c r="Y40" s="11"/>
+      <c r="Z40" s="11"/>
+      <c r="AA40" s="11"/>
+      <c r="AB40" s="11"/>
+      <c r="AC40" s="11"/>
+    </row>
+    <row r="41" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.21698000000000001</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" s="2">
+        <v>10</v>
+      </c>
+      <c r="H41" s="2">
+        <v>12.99212598425197</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="2">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="8">
+      <c r="S41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V41" s="11"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="11"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="11"/>
+      <c r="AB41" s="11"/>
+      <c r="AC41" s="11"/>
+    </row>
+    <row r="42" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.21698000000000001</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" s="2">
+        <v>10</v>
+      </c>
+      <c r="H42" s="2">
+        <v>12.99212598425197</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="2">
+        <v>8</v>
+      </c>
+      <c r="N42" s="3"/>
+      <c r="O42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V42" s="11"/>
+      <c r="W42" s="11"/>
+      <c r="X42" s="11"/>
+      <c r="Y42" s="11"/>
+      <c r="Z42" s="11"/>
+      <c r="AA42" s="11"/>
+      <c r="AB42" s="11"/>
+      <c r="AC42" s="11"/>
+    </row>
+    <row r="43" spans="1:29" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.21698000000000001</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43" s="2">
+        <v>10</v>
+      </c>
+      <c r="H43" s="2">
+        <v>12.99212598425197</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="J43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M43" s="2">
+        <v>1</v>
+      </c>
+      <c r="N43" s="3"/>
+      <c r="O43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V43" s="11"/>
+      <c r="W43" s="11"/>
+      <c r="X43" s="11"/>
+      <c r="Y43" s="11"/>
+      <c r="Z43" s="11"/>
+      <c r="AA43" s="11"/>
+      <c r="AB43" s="11"/>
+      <c r="AC43" s="11"/>
+    </row>
+    <row r="44" spans="1:29" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="18">
+        <v>0.27666666635185178</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" s="18">
+        <v>54</v>
+      </c>
+      <c r="H44" s="18">
+        <v>12.204724410000001</v>
+      </c>
+      <c r="I44" s="18"/>
+      <c r="J44" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="18">
         <v>2</v>
       </c>
-      <c r="H38" s="8">
-        <v>17.519685039370081</v>
-      </c>
-      <c r="I38" s="8">
-        <v>16.51412564754218</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M38" s="8">
-        <v>1</v>
-      </c>
-      <c r="N38" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="O38" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P38" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R38" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S38" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="T38" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U38" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="14"/>
-      <c r="Z38" s="14"/>
-      <c r="AA38" s="14"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P44" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="R44" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="V44" s="11"/>
+      <c r="W44" s="11"/>
+      <c r="X44" s="11"/>
+      <c r="Y44" s="11"/>
+      <c r="Z44" s="11"/>
+      <c r="AA44" s="11"/>
+      <c r="AB44" s="11"/>
+      <c r="AC44" s="11"/>
     </row>
-    <row r="39" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.129</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G39" s="8">
-        <v>8</v>
-      </c>
-      <c r="H39" s="8">
-        <v>15.23622047244095</v>
-      </c>
-      <c r="I39" s="8">
-        <v>16.51412564754218</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M39" s="8">
-        <v>2</v>
-      </c>
-      <c r="N39" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="O39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P39" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R39" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S39" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="T39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U39" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="V39" s="14"/>
-      <c r="W39" s="14"/>
-      <c r="X39" s="14"/>
-      <c r="Y39" s="14"/>
-      <c r="Z39" s="14"/>
-      <c r="AA39" s="14"/>
-    </row>
-    <row r="40" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.39292856978571428</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" s="8">
-        <v>14</v>
-      </c>
-      <c r="H40" s="8">
-        <v>29.055118109999999</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M40" s="8">
-        <v>2</v>
-      </c>
-      <c r="N40" s="8">
-        <v>1</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P40" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R40" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U40" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V40" s="14"/>
-      <c r="W40" s="14"/>
-      <c r="X40" s="14"/>
-      <c r="Y40" s="14"/>
-      <c r="Z40" s="14"/>
-      <c r="AA40" s="14"/>
-    </row>
-    <row r="41" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8">
-        <v>7.5408824058823529E-2</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G41" s="8">
-        <v>34</v>
-      </c>
-      <c r="H41" s="8">
-        <v>17.125984249999998</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M41" s="8">
-        <v>8</v>
-      </c>
-      <c r="N41" s="8">
-        <v>4</v>
-      </c>
-      <c r="O41" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P41" s="8">
-        <v>8</v>
-      </c>
-      <c r="Q41" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R41" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T41" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U41" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V41" s="14"/>
-      <c r="W41" s="14"/>
-      <c r="X41" s="14"/>
-      <c r="Y41" s="14"/>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-    </row>
-    <row r="42" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8">
-        <v>7.5408824058823529E-2</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G42" s="8">
-        <v>34</v>
-      </c>
-      <c r="H42" s="8">
-        <v>17.125984249999998</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M42" s="8">
-        <v>3</v>
-      </c>
-      <c r="N42" s="8">
-        <v>2</v>
-      </c>
-      <c r="O42" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P42" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R42" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T42" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U42" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V42" s="14"/>
-      <c r="W42" s="14"/>
-      <c r="X42" s="14"/>
-      <c r="Y42" s="14"/>
-      <c r="Z42" s="14"/>
-      <c r="AA42" s="14"/>
-    </row>
-    <row r="43" spans="1:27" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.1225409088068182</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G43" s="8">
-        <v>88</v>
-      </c>
-      <c r="H43" s="8">
-        <v>13.38582677</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M43" s="8">
-        <v>2</v>
-      </c>
-      <c r="N43" s="8">
-        <v>1</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P43" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q43" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R43" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T43" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="U43" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="V43" s="14"/>
-      <c r="W43" s="14"/>
-      <c r="X43" s="14"/>
-      <c r="Y43" s="14"/>
-      <c r="Z43" s="14"/>
-      <c r="AA43" s="14"/>
-    </row>
-    <row r="44" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7364,9 +7595,9 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:U43">
-    <sortState ref="A2:Z43">
-      <sortCondition sortBy="cellColor" ref="S1:S43" dxfId="0"/>
+  <autoFilter ref="A1:U44">
+    <sortState ref="A2:U43">
+      <sortCondition ref="A1:A43"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
